--- a/multclass_double_elimination/(31-32人)配布印刷・手作業用3classDoubleElimination.xlsx
+++ b/multclass_double_elimination/(31-32人)配布印刷・手作業用3classDoubleElimination.xlsx
@@ -1594,7 +1594,7 @@
         <is>
           <t>B
 MAIN
-7・8名</t>
+8名</t>
         </is>
       </c>
     </row>
@@ -3514,7 +3514,7 @@
         <is>
           <t>B
 MAIN
-7・8名</t>
+8名</t>
         </is>
       </c>
     </row>
